--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_162_R17.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_162_R17.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5149</v>
+        <v>3.5384</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7955</v>
+        <v>2.0878</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7194</v>
+        <v>1.4506</v>
       </c>
       <c r="G2" t="n">
         <v>1.6897</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4103</v>
+        <v>-0.5663</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0499</v>
+        <v>0.3422</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.9085</v>
       </c>
       <c r="V2" t="n">
         <v>1.719</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4152</v>
+        <v>3.0943</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4276</v>
+        <v>2.8379</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0124</v>
+        <v>0.2565</v>
       </c>
       <c r="G3" t="n">
         <v>2.9418</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7431</v>
+        <v>-2.064</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2284</v>
+        <v>-0.3613</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.9716</v>
+        <v>-1.7027</v>
       </c>
       <c r="V3" t="n">
         <v>2.6805</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2432</v>
+        <v>2.0237</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6828</v>
+        <v>1.329</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5603</v>
+        <v>0.6947</v>
       </c>
       <c r="G4" t="n">
         <v>0.509</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4121</v>
+        <v>0.1926</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5623</v>
+        <v>0.2084</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1502</v>
+        <v>-0.0158</v>
       </c>
       <c r="V4" t="n">
         <v>0.3943</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0058</v>
+        <v>1.6793</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1451</v>
+        <v>1.6169</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1393</v>
+        <v>0.0624</v>
       </c>
       <c r="G5" t="n">
         <v>-0.966</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4225</v>
+        <v>-0.749</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4481</v>
+        <v>0.0237</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9744</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>2.0026</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8203</v>
+        <v>1.4766</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.025</v>
+        <v>0.3289</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8453000000000001</v>
+        <v>1.1477</v>
       </c>
       <c r="G6" t="n">
         <v>1.8527</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7128</v>
+        <v>-1.0565</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0455</v>
+        <v>-0.6917</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6673</v>
+        <v>-0.3648</v>
       </c>
       <c r="V6" t="n">
         <v>1.6083</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.781</v>
+        <v>0.1405</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4208</v>
+        <v>-0.2869</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3602</v>
+        <v>0.4274</v>
       </c>
       <c r="G7" t="n">
         <v>0.1818</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5605</v>
+        <v>-1.201</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3857</v>
+        <v>-0.322</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9462</v>
+        <v>-0.879</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0083</v>
+        <v>-0.1751</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2605</v>
+        <v>-1.7887</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2522</v>
+        <v>1.6137</v>
       </c>
       <c r="G8" t="n">
         <v>-0.584</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3341</v>
+        <v>-1.5009</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.7844</v>
+        <v>-1.3126</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4503</v>
+        <v>-0.1882</v>
       </c>
       <c r="V8" t="n">
         <v>1.214</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2916</v>
+        <v>-0.3588</v>
       </c>
       <c r="E9" t="n">
         <v>-0.2115</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0801</v>
+        <v>-0.1473</v>
       </c>
       <c r="G9" t="n">
         <v>0.0549</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0299</v>
+        <v>-0.0373</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3286</v>
+        <v>0.2614</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8286</v>
+        <v>-0.4912</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1108</v>
+        <v>-0.639</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2822</v>
+        <v>0.1477</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7202</v>
@@ -1234,13 +1234,13 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.3224</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>0.0237</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2117</v>
+        <v>-0.3462</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8867</v>
+        <v>-1.9868</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9891</v>
+        <v>-1.7532</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1024</v>
+        <v>-0.2336</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1053</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0589</v>
+        <v>-0.0413</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8883</v>
+        <v>-0.6524</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.6111</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4606</v>
+        <v>-2.2083</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9096</v>
+        <v>-3.7917</v>
       </c>
       <c r="F12" t="n">
-        <v>1.449</v>
+        <v>1.5834</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6947</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1423</v>
+        <v>0.11</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0009</v>
+        <v>0.1336</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6571</v>
+        <v>-4.0851</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5057</v>
+        <v>-2.2698</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1514</v>
+        <v>-1.8153</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5493</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6929</v>
+        <v>-2.1209</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3364</v>
+        <v>-1.1005</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3566</v>
+        <v>-1.0205</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1829</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.647500000000001</v>
+        <v>2.6475</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.5404</v>
+        <v>-2.5403</v>
       </c>
       <c r="F14" t="n">
-        <v>5.187800000000001</v>
+        <v>5.187900000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.610399999999999</v>
@@ -1546,13 +1546,13 @@
         <v>16.2369</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.3568</v>
+        <v>-9.356999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>-4.1647</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.1925</v>
+        <v>-5.1923</v>
       </c>
       <c r="V14" t="n">
         <v>5.755299999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0166</v>
+        <v>4.5791</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2382</v>
+        <v>3.9459</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7784</v>
+        <v>0.6332</v>
       </c>
       <c r="G15" t="n">
         <v>3.4665</v>
@@ -1624,13 +1624,13 @@
         <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1584</v>
+        <v>1.721</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2794</v>
+        <v>0.9871</v>
       </c>
       <c r="U15" t="n">
-        <v>0.879</v>
+        <v>0.7339</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8534</v>
+        <v>2.9105</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6399</v>
+        <v>1.9322</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2135</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6315</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>2.088</v>
+        <v>1.145</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3214</v>
+        <v>0.6137</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.5313</v>
       </c>
       <c r="V16" t="n">
         <v>2.3969</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6636</v>
+        <v>1.1125</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0851</v>
+        <v>1.1415</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4215</v>
+        <v>-0.029</v>
       </c>
       <c r="G17" t="n">
         <v>2.6708</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>3.0703</v>
+        <v>2.5192</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6384</v>
+        <v>1.6948</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4318</v>
+        <v>0.8244</v>
       </c>
       <c r="V17" t="n">
         <v>-4.5413</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2706</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="E18" t="n">
         <v>0.3697</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.2033</v>
       </c>
       <c r="G18" t="n">
         <v>-2.9063</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9449</v>
+        <v>1.2474</v>
       </c>
       <c r="T18" t="n">
         <v>0.999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.054</v>
+        <v>0.2484</v>
       </c>
       <c r="V18" t="n">
         <v>1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0092</v>
+        <v>0.5611</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0383</v>
+        <v>-1.0585</v>
       </c>
       <c r="F19" t="n">
-        <v>0.029</v>
+        <v>1.6196</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.913</v>
+        <v>-1.6847</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0001</v>
+        <v>-2.0156</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0871</v>
+        <v>0.331</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-1.6594</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9677</v>
+        <v>-1.4684</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>-0.1911</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0179</v>
+        <v>-0.0252</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0323</v>
+        <v>-0.5473</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0502</v>
+        <v>0.5221</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5121</v>
+        <v>1.1736</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1246</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3875</v>
+        <v>0.3949</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1229</v>
+        <v>-0.6269</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7519</v>
+        <v>-0.746</v>
       </c>
       <c r="F20" t="n">
-        <v>0.629</v>
+        <v>0.1191</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9528</v>
+        <v>-0.913</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0025</v>
+        <v>-1.0001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9503</v>
+        <v>0.0871</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9996</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5714</v>
+        <v>-0.9677</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4282</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0468</v>
+        <v>0.0179</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5688</v>
+        <v>-0.0323</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5221</v>
+        <v>0.0502</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9423</v>
+        <v>0.8944</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1221</v>
+        <v>0.4169</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8202</v>
+        <v>0.4775</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8593</v>
+        <v>-0.7792</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1201</v>
+        <v>-1.1057</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2607</v>
+        <v>0.3265</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6847</v>
+        <v>0.9528</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0156</v>
+        <v>0.0025</v>
       </c>
       <c r="I21" t="n">
-        <v>0.331</v>
+        <v>0.9503</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6594</v>
+        <v>0.9996</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4684</v>
+        <v>0.5714</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1911</v>
+        <v>0.4282</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0252</v>
+        <v>-0.0468</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5473</v>
+        <v>-0.5688</v>
       </c>
       <c r="O21" t="n">
         <v>0.5221</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2469</v>
+        <v>0.286</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2829</v>
+        <v>-0.2317</v>
       </c>
       <c r="U21" t="n">
-        <v>0.036</v>
+        <v>0.5177</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W21" t="n">
-        <v>1.214</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3555</v>
+        <v>-1.2547</v>
       </c>
       <c r="E22" t="n">
         <v>-1.1182</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2373</v>
+        <v>-0.1365</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2709</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3888</v>
+        <v>-0.288</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8577</v>
+        <v>-1.4817</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0109</v>
+        <v>-2.8929</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1531</v>
+        <v>1.4112</v>
       </c>
       <c r="G23" t="n">
         <v>0.075</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2992</v>
+        <v>0.6752</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1019</v>
+        <v>0.016</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4011</v>
+        <v>0.6592</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3635</v>
+        <v>-1.9925</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8897</v>
+        <v>-3.4178</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5261</v>
+        <v>1.4253</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7473</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9353</v>
+        <v>1.3063</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3541</v>
+        <v>0.8259</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5812</v>
+        <v>0.4804</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7466</v>
+        <v>-2.3591</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4069</v>
+        <v>-1.053</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3397</v>
+        <v>-1.3061</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6839</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8307</v>
+        <v>-0.4433</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8136</v>
+        <v>-0.4597</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0171</v>
+        <v>0.0165</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5361</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.1369</v>
+        <v>-3.1033</v>
       </c>
       <c r="E26" t="n">
         <v>-1.1851</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9519</v>
+        <v>-1.9182</v>
       </c>
       <c r="G26" t="n">
         <v>-0.9378</v>
@@ -2482,13 +2482,13 @@
         <v>0.6959</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.127</v>
+        <v>-0.0934</v>
       </c>
       <c r="T26" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V26" t="n">
         <v>-1.6083</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.647399999999998</v>
+        <v>-1.8611</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.188199999999999</v>
+        <v>-5.187900000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>2.540300000000001</v>
+        <v>3.326700000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-1.6103</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.05390000000000006</v>
+        <v>-0.05389999999999917</v>
       </c>
       <c r="I27" t="n">
         <v>-1.5563</v>
@@ -2560,13 +2560,13 @@
         <v>11.5978</v>
       </c>
       <c r="S27" t="n">
-        <v>9.357100000000001</v>
+        <v>10.1434</v>
       </c>
       <c r="T27" t="n">
-        <v>5.1925</v>
+        <v>5.1926</v>
       </c>
       <c r="U27" t="n">
-        <v>4.1646</v>
+        <v>4.951000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-5.755299999999999</v>
